--- a/小野町_引継ぎ_整理済/16_町データ依頼/小野町_確認事項の一覧_20261015.xlsx
+++ b/小野町_引継ぎ_整理済/16_町データ依頼/小野町_確認事項の一覧_20261015.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="確認事項の一覧" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'確認事項の一覧'!$A$1:$I$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'確認事項の一覧'!$A$1:$I$74</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -934,19 +934,19 @@
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Ｂ</t>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Ａ</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>当方で一次資料を確認</t>
+          <t>解決済み</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>介護保険法第117条の改正後の項番号（医療計画との整合、地域福祉計画等との調和）</t>
+          <t>県保健医療計画 第8章第9節（過疎・中山間地域の医療）の対象地域</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -956,22 +956,22 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>法令</t>
+          <t>整合</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>Ｅ-4</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>県計画の現物で確定。 無医地区（いわき市1・古殿町3）・準無医地区（いわき市1・田村市3・大熊町1）・へき地診療所27施設（県中は田村市立都路診療所・天栄村国保診療所）のいずれにも本町は含まれない。公立小野町地方綜合病院があることと整合する</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
           <t>―</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>改正により第5項が新設され、現行第5項以降が1つ繰り下がる（新旧対照条文で確認済み）。どの項が何かは条文で確かめる</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>素案の確定まで</t>
         </is>
       </c>
     </row>
@@ -979,19 +979,19 @@
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Ｂ</t>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Ａ</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>当方で一次資料を確認</t>
+          <t>解決済み</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>高齢者住まい法第4条の2・住宅セーフティネット法第6条の条番号</t>
+          <t>県計画 図表12−2−9 の介護施設定員の分類と年次</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1001,22 +1001,22 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>法令</t>
+          <t>記述</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>Ｅ-2の一部</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>見える化の原票で確定。 施設5分類＋居住系3分類で、本町の3つの数値（54・58・53）はいずれも令和3年度の値（県計画の注記は「令和4年時点」）</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
           <t>―</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>検索結果によるものであり、原典で確かめてから本文に書く</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>素案の確定まで</t>
         </is>
       </c>
     </row>
@@ -1024,19 +1024,19 @@
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Ｂ</t>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Ａ</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>当方で一次資料を確認</t>
+          <t>解決済み</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>障害者総合支援法・児童福祉法の調和の規定の項番号</t>
+          <t>本町に介護医療院があるか（県計画 図表12−2−9 の記載との関係）</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1046,22 +1046,22 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>法令</t>
+          <t>記述</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>Ｅ-2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>見える化Ｄ25 で確定。本町に介護医療院はない（平成27〜令和7年度すべて「−」）。県の表の介護医療院58人は、地域密着型介護老人福祉施設の定員が1行下にずれたもの。素案 第2章5 は訂正不要</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
           <t>―</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>支援協議会の意見聴取（第88条第9項・第33条の20第9項）は新旧対照条文で確認済み。調和の規定は未確認</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>骨子の展開まで</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>特別地域加算の対象地域の現行の大臣告示</t>
+          <t>介護保険法第117条の改正後の項番号（医療計画との整合、地域福祉計画等との調和）</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>特定地域</t>
+          <t>法令</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Ｋ-1の一部</t>
+          <t>―</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>ご提供の一覧は平成30年4月時点の民間団体の整理。現行の告示（平成12年厚生省告示第24号の最新改正）で確かめる</t>
+          <t>第2項の号（施策=第5号・目標=第6号）と項の繰り下がりは条文で確定（内部検討7-1・7-2）。残るのは医療計画との整合・老人福祉計画との一体・地域福祉計画等との調和がどの項かで、現行条文の全文が要る。素案は項番号を書いていないため支障はない</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>農林水産省「振興山村一覧表」</t>
+          <t>高齢者住まい法第4条の2・住宅セーフティネット法第6条の条番号</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>特定地域</t>
+          <t>法令</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>検索結果により小野町 旧夏井村・指定番号1179を確かめたにとどまる。一覧の現物で確かめる</t>
+          <t>検索結果によるものであり、原典で確かめてから本文に書く</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>県計画 図表12−2−9 の介護施設定員の分類の取り方</t>
+          <t>障害者総合支援法・児童福祉法の調和の規定の項番号</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1181,22 +1181,22 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>記述</t>
+          <t>法令</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Ｅ-2の一部</t>
+          <t>―</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>見える化システムの分類を当方で確かめる。町固有の事実（本町に介護医療院があるか）は番号34に残す</t>
+          <t>第88条・第33条の20はどちらも新旧とも12項で、項・号の繰り下がりがないことを条文で確定（内部検討8）。現行条文で確かめた番号をそのまま計画期間中使える。調和の規定の番号自体は未確認</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>素案の確定まで</t>
+          <t>骨子の展開まで</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>福島県保健医療計画 第8章第9節（過疎・中山間地域の医療）の対象地域</t>
+          <t>特別地域加算の対象地域の現行の大臣告示</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>整合</t>
+          <t>特定地域</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>Ｋ-1の一部</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>県計画の現物で確かめる。本町が当たるかは特定地域の論点と同じ構図</t>
+          <t>ご提供の一覧は平成30年4月時点の民間団体の整理。現行の告示（平成12年厚生省告示第24号の最新改正）で確かめる</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1249,39 +1249,39 @@
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Ｂ</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>公表資料で先行し、不足分のみ照会</t>
+          <t>当方で一次資料を確認</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>町が市町村高齢者居住安定確保計画・市町村賃貸住宅供給促進計画を定めているか</t>
+          <t>農林水産省「振興山村一覧表」</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>―</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>整合</t>
+          <t>特定地域</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Ｄ-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>県計画は当方が書ける。町が定めているかだけをお尋ねする</t>
+          <t>検索結果により小野町 旧夏井村・指定番号1179を確かめたにとどまる。一覧の現物で確かめる</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>町が医療介護総合確保促進法第5条第1項の市町村計画を定めているか</t>
+          <t>町が市町村高齢者居住安定確保計画・市町村賃貸住宅供給促進計画を定めているか</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1321,12 +1321,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Ｄ-4</t>
+          <t>Ｄ-1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>同上。介護保険法が整合性の確保を求める相手方</t>
+          <t>県計画は当方が書ける。町が定めているかだけをお尋ねする</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>市町村健康増進計画・データヘルス計画・特定健康診査等実施計画の計画期間と所管</t>
+          <t>町が医療介護総合確保促進法第5条第1項の市町村計画を定めているか</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1366,17 +1366,17 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Ｄ-5</t>
+          <t>Ｄ-4</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>国の基本指針が調和の相手方として挙げている。計画名と期間だけで足りる</t>
+          <t>同上。介護保険法が整合性の確保を求める相手方</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>校了まで</t>
+          <t>素案の確定まで</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>住宅確保要配慮者居住支援協議会が町にあるか</t>
+          <t>市町村健康増進計画・データヘルス計画・特定健康診査等実施計画の計画期間と所管</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1406,22 +1406,22 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>住まい</t>
+          <t>整合</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Ｄ-3</t>
+          <t>Ｄ-5</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>福島県居住支援協議会があることは公表資料で分かる。町にあるかだけをお尋ねする。介護保険法第115条の48第5項【新設】の連携の相手方</t>
+          <t>国の基本指針が調和の相手方として挙げている。計画名と期間だけで足りる</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>素案の確定まで</t>
+          <t>校了まで</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>町営住宅・公営住宅の高齢者向け住戸の有無とバリアフリー化の状況</t>
+          <t>住宅確保要配慮者居住支援協議会が町にあるか</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1456,17 +1456,17 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Ｄ-2</t>
+          <t>Ｄ-3</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>県計画の中通りの課題「借家でバリアフリー化割合が低い」に対応。町の住戸の状況だけをお尋ねする</t>
+          <t>福島県居住支援協議会があることは公表資料で分かる。町にあるかだけをお尋ねする。介護保険法第115条の48第5項【新設】の連携の相手方</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>校了まで</t>
+          <t>素案の確定まで</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>町内の在宅療養支援病院・診療所2か所の内訳</t>
+          <t>町営住宅・公営住宅の高齢者向け住戸の有無とバリアフリー化の状況</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1496,22 +1496,22 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>医療</t>
+          <t>住まい</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Ｅ-3</t>
+          <t>Ｄ-2</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>箇所数は県計画で分かる（令和3年3月末）。内訳と現況だけをお尋ねする</t>
+          <t>県計画の中通りの課題「借家でバリアフリー化割合が低い」に対応。町の住戸の状況だけをお尋ねする</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>素案の確定まで</t>
+          <t>校了まで</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>本町の難病患者の把握状況と県中保健所・難病相談支援センターとの連携</t>
+          <t>町内の在宅療養支援病院・診療所2か所の内訳</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>障がい</t>
+          <t>医療</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Ｆ-3</t>
+          <t>Ｅ-3</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>県全体の患者数・相談件数は県計画で分かる。町の把握と連携だけをお尋ねする</t>
+          <t>箇所数は県計画で分かる（令和3年3月末）。内訳と現況だけをお尋ねする</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>骨子の展開まで</t>
+          <t>素案の確定まで</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>障がいのある方の住まいの状況（グループホームの定員、公営住宅の入居、住宅セーフティネット制度の利用）</t>
+          <t>本町の難病患者の把握状況と県中保健所・難病相談支援センターとの連携</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Ｆ-4</t>
+          <t>Ｆ-3</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>制度の枠組みは公表資料で書ける。町の実績だけをお尋ねする</t>
+          <t>県全体の患者数・相談件数は県計画で分かる。町の把握と連携だけをお尋ねする</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1609,19 +1609,19 @@
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>町の回答・内部データが必要</t>
+          <t>公表資料で先行し、不足分のみ照会</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の残高（各年度末。基金運用状況調書、または決算書の財産に関する調書）</t>
+          <t>障がいのある方の住まいの状況（グループホームの定員、公営住宅の入居、住宅セーフティネット制度の利用）</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>保険料</t>
+          <t>障がい</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Ａ-1</t>
+          <t>Ｆ-4</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>保険料の最大の論点。取崩しなし6,053円／12,000千円で6,000円弱／35,000千円で5,808円。取崩しが7年間0であったと分かり、残高が想定より大きい可能性がある</t>
+          <t>制度の枠組みは公表資料で書ける。町の実績だけをお尋ねする</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11月6日まで</t>
+          <t>骨子の展開まで</t>
         </is>
       </c>
     </row>
@@ -1666,32 +1666,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>協議会の開催回数と印刷日数の確定</t>
+          <t>介護給付費準備基金の残高（各年度末。基金運用状況調書、または決算書の財産に関する調書）</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>町（判断）</t>
+          <t>町</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>工程</t>
+          <t>保険料</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Ｂ-1</t>
+          <t>Ａ-1</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>工程全体の起点。案A（4回）なら第1回の期限は11月6日、案B（3回）なら11月27日、案D（3回・印刷18日）なら12月4日</t>
+          <t>保険料の最大の論点。取崩しなし6,053円／12,000千円で6,000円弱／35,000千円で5,808円。取崩しが7年間0であったと分かり、残高が想定より大きい可能性がある</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>最優先</t>
+          <t>11月6日まで</t>
         </is>
       </c>
     </row>
@@ -1711,32 +1711,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>令和9〜11年度に65歳に達する障がい福祉サービス利用者の一覧</t>
+          <t>協議会の開催回数と印刷日数の確定</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>町（判断）</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>両計画</t>
+          <t>工程</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Ａ-4・接点2</t>
+          <t>Ｂ-1</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>これ1件で両計画の接点の2・4・7・9がまとめて片付く</t>
+          <t>工程全体の起点。案A（4回）なら第1回の期限は11月6日、案B（3回）なら11月27日、案D（3回・印刷18日）なら12月4日</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10月28日まで</t>
+          <t>最優先</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>介護保険の適用除外に当たる方の有無</t>
+          <t>令和9〜11年度に65歳に達する障がい福祉サービス利用者の一覧</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1766,17 +1766,17 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>保険料</t>
+          <t>両計画</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>接点1</t>
+          <t>Ａ-4・接点2</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>第1号被保険者数＝保険料の分母。該当者がいると保険料が動く。該当なしの確認でもよい</t>
+          <t>これ1件で両計画の接点の2・4・7・9がまとめて片付く</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>通いの場の箇所数・参加者数（週1回以上／月1回以上の別）と、訪問型サービスＢ・通所型サービスＢが令和7年度に0円になった経緯</t>
+          <t>介護保険の適用除外に当たる方の有無</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1811,22 +1811,22 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>施策</t>
+          <t>保険料</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Ａ-2</t>
+          <t>接点1</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>素案が事実と違う記述を含んだまま協議会に出ることになる。成果指標の現状値にも使う</t>
+          <t>第1号被保険者数＝保険料の分母。該当者がいると保険料が動く。該当なしの確認でもよい</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11月6日まで</t>
+          <t>10月28日まで</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>町内の有料老人ホーム（老人福祉法第29条第1項の届出）とサービス付き高齢者向け住宅の有無・入居定員</t>
+          <t>通いの場の箇所数・参加者数（週1回以上／月1回以上の別）と、訪問型サービスＢ・通所型サービスＢが令和7年度に0円になった経緯</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1856,17 +1856,17 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>住まい</t>
+          <t>施策</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Ｈ-1・Ａ-3</t>
+          <t>Ａ-2</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>法定の勘案事項（介保法第117条第5項第1号）。県高齢者居住安定確保計画の【基本事項】②でも市町村に求められている。該当なしの確認でもよい</t>
+          <t>素案が事実と違う記述を含んだまま協議会に出ることになる。成果指標の現状値にも使う</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -1891,27 +1891,27 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>保険料の方針（基金取崩額、所得段階の数と率）</t>
+          <t>町内の有料老人ホーム（老人福祉法第29条第1項の届出）とサービス付き高齢者向け住宅の有無・入居定員</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>町（判断）</t>
+          <t>町</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>保険料</t>
+          <t>住まい</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Ｂ-2</t>
+          <t>Ｈ-1・Ａ-3</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>協議会にお諮りする前提。所得段階別被保険者数は受領済み（令和8年4月1日現在3,436人・13段階）</t>
+          <t>法定の勘案事項（介保法第117条第5項第1号）。県高齢者居住安定確保計画の【基本事項】②でも市町村に求められている。該当なしの確認でもよい</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -1936,32 +1936,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>地域支援事業13事業の量（事業費ではなく量）</t>
+          <t>保険料の方針（基金取崩額、所得段階の数と率）</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>町（判断）</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>算定</t>
+          <t>保険料</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Ａ-7</t>
+          <t>Ｂ-2</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項第2号の法定記載事項。事業費は交付金実績報告で取れたが、量は町の実績でないと取れない</t>
+          <t>協議会にお諮りする前提。所得段階別被保険者数は受領済み（令和8年4月1日現在3,436人・13段階）</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>素案の確定まで</t>
+          <t>11月6日まで</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>令和7年8〜9月の認定者数の計上方法の変更の有無</t>
+          <t>地域支援事業13事業の量（事業費ではなく量）</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Ａ-5</t>
+          <t>Ａ-7</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>認定者数の推計の前提。令和8年3月末の認定者数は792人で前年944人から16.1％減り、減少が令和7年9月審査分の1か月に集中</t>
+          <t>介護保険法第117条第2項第2号の法定記載事項。事業費は交付金実績報告で取れたが、量は町の実績でないと取れない</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>本町に介護医療院があるか（県計画 図表12−2−9 の記載との関係）</t>
+          <t>令和7年8〜9月の認定者数の計上方法の変更の有無</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2036,17 +2036,17 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>記述</t>
+          <t>算定</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Ｅ-2</t>
+          <t>Ａ-5</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>県の表に本町の介護医療院58人とあり、素案の地域密着型介護老人福祉施設58人と同じ数字。どちらが誤りとも断定しない</t>
+          <t>認定者数の推計の前提。令和8年3月末の認定者数は792人で前年944人から16.1％減り、減少が令和7年9月審査分の1か月に集中</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>第6章11（将来に向けたサービス提供体制の確保）</t>
+          <t>第6章12（将来に向けたサービス提供体制の確保）</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -3286,32 +3286,32 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>福島県高齢者居住安定確保計画の改定の予定と内容</t>
+          <t>老人福祉事業の量の目標の前提となる量（養護老人ホーム・軽費老人ホームの本町からの入所者数と老人福祉センターの利用状況）</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>県</t>
+          <t>町</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>整合</t>
+          <t>記述</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Ｄ-6の残り</t>
+          <t>―</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>計画期間が令和8年度で満了し、本計画期間の初日には現行計画が存在しない</t>
+          <t>老人福祉法第20条の8第2項の法定記載事項。介護保険に重ならない3種が素案で未確定（第6章9）</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>最優先</t>
+          <t>素案の確定まで</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>新たな福島県地域医療構想の策定状況</t>
+          <t>福島県高齢者居住安定確保計画の改定の予定と内容</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3346,12 +3346,12 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Ｅ-1</t>
+          <t>Ｄ-6の残り</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>目標年が令和7年。慢性期病床の動きは介護サービス需要に直接効く</t>
+          <t>計画期間が令和8年度で満了し、本計画期間の初日には現行計画が存在しない</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>介護保険法第117条第14項の意見聴取の時期と様式</t>
+          <t>新たな福島県地域医療構想の策定状況</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3386,17 +3386,17 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>手続</t>
+          <t>整合</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Ｋ-3・Ｃ-1</t>
+          <t>Ｅ-1</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>計画を定めるにあたりあらかじめ県の意見を聴かなければならない。中長期推計が対象に加わった</t>
+          <t>目標年が令和7年。慢性期病床の動きは介護サービス需要に直接効く</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>特定地域の省令の基準・県が定める時期・町への意向照会の時期</t>
+          <t>介護保険法第117条第14項の意見聴取の時期と様式</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3431,22 +3431,22 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>特定地域</t>
+          <t>手続</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Ｋ-1・Ｃ-3</t>
+          <t>Ｋ-3・Ｃ-1</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>特定地域サービスの適用</t>
+          <t>計画を定めるにあたりあらかじめ県の意見を聴かなければならない。中長期推計が対象に加わった</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>最優先</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>県中医療圏における精神科医療の体制（にも包括の協議の場の設置状況）</t>
+          <t>特定地域の省令の基準・県が定める時期・町への意向照会の時期</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3476,22 +3476,22 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>障がい</t>
+          <t>特定地域</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Ｆ-1</t>
+          <t>Ｋ-1・Ｃ-3</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>にも包括の成果目標は県が設定し、町は活動指標を置く</t>
+          <t>特定地域サービスの適用</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>最優先</t>
+          <t>高</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>医療的ケア児等支援センターの名称変更・業務の追加と、医療的ケア児等支援地域協議会の設置予定。市町村の「協議の場」の成果目標の扱い</t>
+          <t>県中医療圏における精神科医療の体制（にも包括の協議の場の設置状況）</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Ｋ-2の残り・Ｆ-2</t>
+          <t>Ｆ-1</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>県保健医療計画より後の改正。コーディネーター配置促進の具体の内容も</t>
+          <t>にも包括の成果目標は県が設定し、町は活動指標を置く</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>調整交付金の算定方法と本町の交付割合の見通し</t>
+          <t>医療的ケア児等支援センターの名称変更・業務の追加と、医療的ケア児等支援地域協議会の設置予定。市町村の「協議の場」の成果目標の扱い</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -3566,22 +3566,22 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>保険料</t>
+          <t>障がい</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Ｃ-2</t>
+          <t>Ｋ-2の残り・Ｆ-2</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>本計画の算定にはこの勘案を織り込んでいない</t>
+          <t>県保健医療計画より後の改正。コーディネーター配置促進の具体の内容も</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>最優先</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>社会福祉法第106条の6の小規模市町村の省令の基準</t>
+          <t>調整交付金の算定方法と本町の交付割合の見通し</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -3611,22 +3611,22 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>整合</t>
+          <t>保険料</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Ｋ-4</t>
+          <t>Ｃ-2</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>該当する場合、両計画の実施体制が変わる</t>
+          <t>本計画の算定にはこの勘案を織り込んでいない</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>夜間対応型訪問介護の経過措置の内容と期間</t>
+          <t>社会福祉法第106条の6の小規模市町村の省令の基準</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -3656,17 +3656,17 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>算定</t>
+          <t>整合</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Ｋ-5・Ｃ-6</t>
+          <t>Ｋ-4</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>本町は0.0人／月のため数値への影響はない。本文の書きぶり</t>
+          <t>該当する場合、両計画の実施体制が変わる</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>第5次福島県障がい者計画の次期計画の策定状況</t>
+          <t>夜間対応型訪問介護の経過措置の内容と期間</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -3701,22 +3701,22 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>障がい</t>
+          <t>算定</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Ｆ-6</t>
+          <t>Ｋ-5・Ｃ-6</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>県障がい者計画は令和9年度で満了する</t>
+          <t>本町は0.0人／月のため数値への影響はない。本文の書きぶり</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
     </row>
@@ -3736,37 +3736,82 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>第5次福島県障がい者計画の次期計画の策定状況</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>県</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>障がい</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Ｆ-6</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>県障がい者計画は令和9年度で満了する</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="54" customHeight="1">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>町の回答・内部データが必要</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
           <t>第10期基本指針（介護）・第8期基本指針の再改正の範囲と時期</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>県</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>整合</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>Ｋ-6・Ｃ-5</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>第10期基本指針は令和9年1月告示の予定</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I73"/>
+  <autoFilter ref="A1:I74"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/小野町_引継ぎ_整理済/16_町データ依頼/小野町_確認事項の一覧_20261015.xlsx
+++ b/小野町_引継ぎ_整理済/16_町データ依頼/小野町_確認事項の一覧_20261015.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="確認事項の一覧" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'確認事項の一覧'!$A$1:$I$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'確認事項の一覧'!$A$1:$I$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1294,44 +1294,44 @@
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Ｂ</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>公表資料で先行し、不足分のみ照会</t>
+          <t>当方で一次資料を確認</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>町が市町村高齢者居住安定確保計画・市町村賃貸住宅供給促進計画を定めているか</t>
+          <t>手話に関する施策の推進に関する法律の法律番号と施行日</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>―</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>整合</t>
+          <t>法令</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Ｄ-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>県計画は当方が書ける。町が定めているかだけをお尋ねする</t>
+          <t>障がい素案 第2部第4章の根拠。令和7年6月成立までは確かめたが、法律番号が未確認。町条例（令和7年4月）とあわせて書く</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>素案の確定まで</t>
+          <t>骨子の展開まで</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>町が医療介護総合確保促進法第5条第1項の市町村計画を定めているか</t>
+          <t>町が市町村高齢者居住安定確保計画・市町村賃貸住宅供給促進計画を定めているか</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1366,12 +1366,12 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Ｄ-4</t>
+          <t>Ｄ-1</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>同上。介護保険法が整合性の確保を求める相手方</t>
+          <t>県計画は当方が書ける。町が定めているかだけをお尋ねする</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>市町村健康増進計画・データヘルス計画・特定健康診査等実施計画の計画期間と所管</t>
+          <t>町が医療介護総合確保促進法第5条第1項の市町村計画を定めているか</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1411,17 +1411,17 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Ｄ-5</t>
+          <t>Ｄ-4</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>国の基本指針が調和の相手方として挙げている。計画名と期間だけで足りる</t>
+          <t>同上。介護保険法が整合性の確保を求める相手方</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>校了まで</t>
+          <t>素案の確定まで</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>住宅確保要配慮者居住支援協議会が町にあるか</t>
+          <t>市町村健康増進計画・データヘルス計画・特定健康診査等実施計画の計画期間と所管</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1451,22 +1451,22 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>住まい</t>
+          <t>整合</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Ｄ-3</t>
+          <t>Ｄ-5</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>福島県居住支援協議会があることは公表資料で分かる。町にあるかだけをお尋ねする。介護保険法第115条の48第5項【新設】の連携の相手方</t>
+          <t>国の基本指針が調和の相手方として挙げている。計画名と期間だけで足りる</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>素案の確定まで</t>
+          <t>校了まで</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>町営住宅・公営住宅の高齢者向け住戸の有無とバリアフリー化の状況</t>
+          <t>住宅確保要配慮者居住支援協議会が町にあるか</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1501,17 +1501,17 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Ｄ-2</t>
+          <t>Ｄ-3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>県計画の中通りの課題「借家でバリアフリー化割合が低い」に対応。町の住戸の状況だけをお尋ねする</t>
+          <t>福島県居住支援協議会があることは公表資料で分かる。町にあるかだけをお尋ねする。介護保険法第115条の48第5項【新設】の連携の相手方</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>校了まで</t>
+          <t>素案の確定まで</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>町内の在宅療養支援病院・診療所2か所の内訳</t>
+          <t>町営住宅・公営住宅の高齢者向け住戸の有無とバリアフリー化の状況</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>医療</t>
+          <t>住まい</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Ｅ-3</t>
+          <t>Ｄ-2</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>箇所数は県計画で分かる（令和3年3月末）。内訳と現況だけをお尋ねする</t>
+          <t>県計画の中通りの課題「借家でバリアフリー化割合が低い」に対応。町の住戸の状況だけをお尋ねする</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>素案の確定まで</t>
+          <t>校了まで</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>本町の難病患者の把握状況と県中保健所・難病相談支援センターとの連携</t>
+          <t>町内の在宅療養支援病院・診療所2か所の内訳</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1586,22 +1586,22 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>障がい</t>
+          <t>医療</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Ｆ-3</t>
+          <t>Ｅ-3</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>県全体の患者数・相談件数は県計画で分かる。町の把握と連携だけをお尋ねする</t>
+          <t>箇所数は県計画で分かる（令和3年3月末）。内訳と現況だけをお尋ねする</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>骨子の展開まで</t>
+          <t>素案の確定まで</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>障がいのある方の住まいの状況（グループホームの定員、公営住宅の入居、住宅セーフティネット制度の利用）</t>
+          <t>本町の難病患者の把握状況と県中保健所・難病相談支援センターとの連携</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1636,12 +1636,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Ｆ-4</t>
+          <t>Ｆ-3</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>制度の枠組みは公表資料で書ける。町の実績だけをお尋ねする</t>
+          <t>県全体の患者数・相談件数は県計画で分かる。町の把握と連携だけをお尋ねする</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1654,19 +1654,19 @@
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>町の回答・内部データが必要</t>
+          <t>公表資料で先行し、不足分のみ照会</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の残高（各年度末。基金運用状況調書、または決算書の財産に関する調書）</t>
+          <t>障がいのある方の住まいの状況（グループホームの定員、公営住宅の入居、住宅セーフティネット制度の利用）</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1676,22 +1676,22 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>保険料</t>
+          <t>障がい</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Ａ-1</t>
+          <t>Ｆ-4</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>保険料の最大の論点。取崩しなし6,053円／12,000千円で6,000円弱／35,000千円で5,808円。取崩しが7年間0であったと分かり、残高が想定より大きい可能性がある</t>
+          <t>制度の枠組みは公表資料で書ける。町の実績だけをお尋ねする</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11月6日まで</t>
+          <t>骨子の展開まで</t>
         </is>
       </c>
     </row>
@@ -1711,32 +1711,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>協議会の開催回数と印刷日数の確定</t>
+          <t>介護給付費準備基金の残高（各年度末。基金運用状況調書、または決算書の財産に関する調書）</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>町（判断）</t>
+          <t>町</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>工程</t>
+          <t>保険料</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Ｂ-1</t>
+          <t>Ａ-1</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>工程全体の起点。案A（4回）なら第1回の期限は11月6日、案B（3回）なら11月27日、案D（3回・印刷18日）なら12月4日</t>
+          <t>保険料の最大の論点。取崩しなし6,053円／12,000千円で6,000円弱／35,000千円で5,808円。取崩しが7年間0であったと分かり、残高が想定より大きい可能性がある</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>最優先</t>
+          <t>11月6日まで</t>
         </is>
       </c>
     </row>
@@ -1756,32 +1756,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>令和9〜11年度に65歳に達する障がい福祉サービス利用者の一覧</t>
+          <t>協議会の開催回数と印刷日数の確定</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>町（判断）</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>両計画</t>
+          <t>工程</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Ａ-4・接点2</t>
+          <t>Ｂ-1</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>これ1件で両計画の接点の2・4・7・9がまとめて片付く</t>
+          <t>工程全体の起点。案A（4回）なら第1回の期限は11月6日、案B（3回）なら11月27日、案D（3回・印刷18日）なら12月4日</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10月28日まで</t>
+          <t>最優先</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>介護保険の適用除外に当たる方の有無</t>
+          <t>令和9〜11年度に65歳に達する障がい福祉サービス利用者の一覧</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1811,17 +1811,17 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>保険料</t>
+          <t>両計画</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>接点1</t>
+          <t>Ａ-4・接点2</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>第1号被保険者数＝保険料の分母。該当者がいると保険料が動く。該当なしの確認でもよい</t>
+          <t>これ1件で両計画の接点の2・4・7・9がまとめて片付く</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>通いの場の箇所数・参加者数（週1回以上／月1回以上の別）と、訪問型サービスＢ・通所型サービスＢが令和7年度に0円になった経緯</t>
+          <t>介護保険の適用除外に当たる方の有無</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1856,22 +1856,22 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>施策</t>
+          <t>保険料</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Ａ-2</t>
+          <t>接点1</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>素案が事実と違う記述を含んだまま協議会に出ることになる。成果指標の現状値にも使う</t>
+          <t>第1号被保険者数＝保険料の分母。該当者がいると保険料が動く。該当なしの確認でもよい</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>11月6日まで</t>
+          <t>10月28日まで</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>町内の有料老人ホーム（老人福祉法第29条第1項の届出）とサービス付き高齢者向け住宅の有無・入居定員</t>
+          <t>通いの場の箇所数・参加者数（週1回以上／月1回以上の別）と、訪問型サービスＢ・通所型サービスＢが令和7年度に0円になった経緯</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1901,17 +1901,17 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>住まい</t>
+          <t>施策</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Ｈ-1・Ａ-3</t>
+          <t>Ａ-2</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>法定の勘案事項（介保法第117条第5項第1号）。県高齢者居住安定確保計画の【基本事項】②でも市町村に求められている。該当なしの確認でもよい</t>
+          <t>素案が事実と違う記述を含んだまま協議会に出ることになる。成果指標の現状値にも使う</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -1936,27 +1936,27 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>保険料の方針（基金取崩額、所得段階の数と率）</t>
+          <t>町内の有料老人ホーム（老人福祉法第29条第1項の届出）とサービス付き高齢者向け住宅の有無・入居定員</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>町（判断）</t>
+          <t>町</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>保険料</t>
+          <t>住まい</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Ｂ-2</t>
+          <t>Ｈ-1・Ａ-3</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>協議会にお諮りする前提。所得段階別被保険者数は受領済み（令和8年4月1日現在3,436人・13段階）</t>
+          <t>法定の勘案事項（介保法第117条第5項第1号）。県高齢者居住安定確保計画の【基本事項】②でも市町村に求められている。該当なしの確認でもよい</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -1981,32 +1981,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>地域支援事業13事業の量（事業費ではなく量）</t>
+          <t>保険料の方針（基金取崩額、所得段階の数と率）</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>町（判断）</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>算定</t>
+          <t>保険料</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Ａ-7</t>
+          <t>Ｂ-2</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項第2号の法定記載事項。事業費は交付金実績報告で取れたが、量は町の実績でないと取れない</t>
+          <t>協議会にお諮りする前提。所得段階別被保険者数は受領済み（令和8年4月1日現在3,436人・13段階）</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>素案の確定まで</t>
+          <t>11月6日まで</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>令和7年8〜9月の認定者数の計上方法の変更の有無</t>
+          <t>地域支援事業13事業の量（事業費ではなく量）</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2041,12 +2041,12 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Ａ-5</t>
+          <t>Ａ-7</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>認定者数の推計の前提。令和8年3月末の認定者数は792人で前年944人から16.1％減り、減少が令和7年9月審査分の1か月に集中</t>
+          <t>介護保険法第117条第2項第2号の法定記載事項。事業費は交付金実績報告で取れたが、量は町の実績でないと取れない</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>振興山村（旧夏井村）の区域が現在のどの大字に当たるか。その区域の事業所と特別地域加算の算定実績</t>
+          <t>令和7年8〜9月の認定者数の計上方法の変更の有無</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>特定地域</t>
+          <t>算定</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Ｈ-6・Ａ-9</t>
+          <t>Ａ-5</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>昭和25年2月1日時点の市町村境界が基準のため、町でなければ分からない</t>
+          <t>認定者数の推計の前提。令和8年3月末の認定者数は792人で前年944人から16.1％減り、減少が令和7年9月審査分の1か月に集中</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>特定地域の指定についての町の意向</t>
+          <t>振興山村（旧夏井村）の区域が現在のどの大字に当たるか。その区域の事業所と特別地域加算の算定実績</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>町（判断）</t>
+          <t>町</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Ｂ-4</t>
+          <t>Ｈ-6・Ａ-9</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>手続は市町村が要否を検討し、その意向を踏まえて県が定める。県からの照会を待ってからでは間に合わない</t>
+          <t>昭和25年2月1日時点の市町村境界が基準のため、町でなければ分からない</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>認知症の人及びその家族等の意見を聴く方法</t>
+          <t>特定地域の指定についての町の意向</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2171,17 +2171,17 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>手続</t>
+          <t>特定地域</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Ｂ-3</t>
+          <t>Ｂ-4</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>認知症基本法第13条第3項が準用する第12条第3項の努力義務</t>
+          <t>手続は市町村が要否を検討し、その意向を踏まえて県が定める。県からの照会を待ってからでは間に合わない</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>4つの場面の目指すべき姿（退院支援・日常の療養支援・急変時の対応・看取り）</t>
+          <t>認知症の人及びその家族等の意見を聴く方法</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>町・関係機関</t>
+          <t>町（判断）</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>施策</t>
+          <t>手続</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Ｂ-5・Ｅ-4</t>
+          <t>Ｂ-3</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>交付金 評価指標 目標Ⅲ−（ⅰ）−1が設定を求めている。県保健医療計画 第8章第12節が手がかりになる（急変時の消防、看取りのＡＣＰ）</t>
+          <t>認知症基本法第13条第3項が準用する第12条第3項の努力義務</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>11月6日まで</t>
+          <t>素案の確定まで</t>
         </is>
       </c>
     </row>
@@ -2251,32 +2251,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>支援協議会（自立支援協議会）・支援会議の設置の有無</t>
+          <t>4つの場面の目指すべき姿（退院支援・日常の療養支援・急変時の対応・看取り）</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>町・関係機関</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>手続</t>
+          <t>施策</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Ｈ-5</t>
+          <t>Ｂ-5・Ｅ-4</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>計画の策定手続そのもの。設置していれば策定・変更にあたり意見を聴くよう努めなければならない</t>
+          <t>交付金 評価指標 目標Ⅲ−（ⅰ）−1が設定を求めている。県保健医療計画 第8章第12節が手がかりになる（急変時の消防、看取りのＡＣＰ）</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>10月28日まで</t>
+          <t>11月6日まで</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>認知症初期集中支援推進事業の実施体制</t>
+          <t>支援協議会（自立支援協議会）・支援会議の設置の有無</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2306,22 +2306,22 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>施策</t>
+          <t>手続</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Ａ-6</t>
+          <t>Ｈ-5</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>交付金実績報告では令和6・7年度とも0円</t>
+          <t>計画の策定手続そのもの。設置していれば策定・変更にあたり意見を聴くよう努めなければならない</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>素案の確定まで</t>
+          <t>10月28日まで</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>地域密着型通所介護の実績が0になった理由</t>
+          <t>認知症初期集中支援推進事業の実施体制</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>記述</t>
+          <t>施策</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Ａ-8</t>
+          <t>Ａ-6</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>令和3年度14件→令和6・7年度0件。事業所の休廃止か、利用が他に移ったか</t>
+          <t>交付金実績報告では令和6・7年度とも0円</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>要介護認定の適正化の内容（認定調査の委託の有無と点検件数）</t>
+          <t>地域密着型通所介護の実績が0になった理由</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2396,17 +2396,17 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>交付金</t>
+          <t>記述</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Ａ-10</t>
+          <t>Ａ-8</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>交付金の得点</t>
+          <t>令和3年度14件→令和6・7年度0件。事業所の休廃止か、利用が他に移ったか</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>町の面積と町営バス・デマンド型交通の運行状況</t>
+          <t>要介護認定の適正化の内容（認定調査の委託の有無と点検件数）</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2441,22 +2441,22 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>記述</t>
+          <t>交付金</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Ａ-11</t>
+          <t>Ａ-10</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>第1章5（日常生活圏域）。特定地域の指標「75歳以上人口密度」の分母にもなる</t>
+          <t>交付金の得点</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>校了まで</t>
+          <t>素案の確定まで</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>社会福祉法人等による利用者負担軽減の実績</t>
+          <t>町の面積と町営バス・デマンド型交通の運行状況</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Ａ-12</t>
+          <t>Ａ-11</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>高額介護サービス費と負担限度額認定は年報で取れたため、残りはこれだけ</t>
+          <t>第1章5（日常生活圏域）。特定地域の指標「75歳以上人口密度」の分母にもなる</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>介護用品給付券等の町単独事業の財源科目と補助対象の可否</t>
+          <t>社会福祉法人等による利用者負担軽減の実績</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Ａ-13</t>
+          <t>Ａ-12</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>第5章 基本目標2（家族介護支援）</t>
+          <t>高額介護サービス費と負担限度額認定は年報で取れたため、残りはこれだけ</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>若年性認知症（65歳未満）の町内の把握状況</t>
+          <t>介護用品給付券等の町単独事業の財源科目と補助対象の可否</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2576,17 +2576,17 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>施策</t>
+          <t>記述</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Ａ-14</t>
+          <t>Ａ-13</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>第2号被保険者の認定者は令和8年3月末で9人</t>
+          <t>第5章 基本目標2（家族介護支援）</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>町内事業所の休廃止を早く知る仕組みの現状</t>
+          <t>若年性認知症（65歳未満）の町内の把握状況</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Ａ-15</t>
+          <t>Ａ-14</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>第6章12（将来に向けたサービス提供体制の確保）</t>
+          <t>第2号被保険者の認定者は令和8年3月末で9人</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>第3期地域福祉計画における包括的な支援体制の記載と、町の相談支援・地域づくりの実施体制</t>
+          <t>町内事業所の休廃止を早く知る仕組みの現状</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2666,22 +2666,22 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>整合</t>
+          <t>施策</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Ｈ-2</t>
+          <t>Ａ-15</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>社会福祉法第106条の6（小規模市町村）との役割分担</t>
+          <t>第6章12（将来に向けたサービス提供体制の確保）</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>素案の確定まで</t>
+          <t>校了まで</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>成年後見の中核機関の体制と、地域権利擁護相談支援センターへの移行の意向</t>
+          <t>第3期地域福祉計画における包括的な支援体制の記載と、町の相談支援・地域づくりの実施体制</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Ｈ-3</t>
+          <t>Ｈ-2</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>令和8年法律第51号・第45号</t>
+          <t>社会福祉法第106条の6（小規模市町村）との役割分担</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>家庭裁判所から町へ本人の状況について照会を受けた実績と手順</t>
+          <t>成年後見の中核機関の体制と、地域権利擁護相談支援センターへの移行の意向</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2761,17 +2761,17 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Ｈ-4</t>
+          <t>Ｈ-3</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>令和8年法律第45号（市町村長等への意見の求め）</t>
+          <t>令和8年法律第51号・第45号</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>校了まで</t>
+          <t>素案の確定まで</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>第2号被保険者の認定者のうち障がい福祉サービスの受給者証をお持ちの方</t>
+          <t>家庭裁判所から町へ本人の状況について照会を受けた実績と手順</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2801,22 +2801,22 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>両計画</t>
+          <t>整合</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>接点3</t>
+          <t>Ｈ-4</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>両計画の接点1。該当なしの確認でもよい</t>
+          <t>令和8年法律第45号（市町村長等への意見の求め）</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>素案の確定まで</t>
+          <t>校了まで</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>町内事業所の事業所番号と指定の種類（共生型サービス・基準該当障害福祉サービス）</t>
+          <t>第2号被保険者の認定者のうち障がい福祉サービスの受給者証をお持ちの方</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>接点4</t>
+          <t>接点3</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>両計画の接点6。同じ事業所が両計画に現れるため名寄せが要る</t>
+          <t>両計画の接点1。該当なしの確認でもよい</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>計画相談支援の実利用者数のうち65歳以上の方</t>
+          <t>町内事業所の事業所番号と指定の種類（共生型サービス・基準該当障害福祉サービス）</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>接点5</t>
+          <t>接点4</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>両計画の接点8（居宅介護支援への引継ぎ）</t>
+          <t>両計画の接点6。同じ事業所が両計画に現れるため名寄せが要る</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>骨子の展開まで</t>
+          <t>素案の確定まで</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>医療的ケア児等の人数と状況（18歳以上の医療的ケア者・重症心身障害者を含む）と個別避難計画の作成状況</t>
+          <t>計画相談支援の実利用者数のうち65歳以上の方</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2936,22 +2936,22 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>障がい</t>
+          <t>両計画</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Ｆ-5</t>
+          <t>接点5</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>医療的ケア児支援法の改正（令和9年4月1日施行）。センターの業務に個別避難計画の作成への協力が加わる</t>
+          <t>両計画の接点8（居宅介護支援への引継ぎ）</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>10月28日まで</t>
+          <t>骨子の展開まで</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>障がいサービス別実績・支給決定量と実利用量・町内外事業所別の利用者数</t>
+          <t>医療的ケア児等の人数と状況（18歳以上の医療的ケア者・重症心身障害者を含む）と個別避難計画の作成状況</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>番号3</t>
+          <t>Ｆ-5</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>障がい 第3部第2章（見込量）の全体</t>
+          <t>医療的ケア児支援法の改正（令和9年4月1日施行）。センターの業務に個別避難計画の作成への協力が加わる</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>施設入所者数の令和7年度末確定値と、現行計画（第7期・第3期）の成果目標の実績値</t>
+          <t>障がいサービス別実績・支給決定量と実利用量・町内外事業所別の利用者数</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3031,12 +3031,12 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>番号4</t>
+          <t>番号3</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>成果目標①。令和11年度末を基準に目標を定める</t>
+          <t>障がい 第3部第2章（見込量）の全体</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>今期アンケート調査の結果と関係者団体等ヒアリングの結果</t>
+          <t>施設入所者数の令和7年度末確定値と、現行計画（第7期・第3期）の成果目標の実績値</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3076,17 +3076,17 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>番号13</t>
+          <t>番号4</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>現状と課題の記述の根拠そのもの</t>
+          <t>成果目標①。令和11年度末を基準に目標を定める</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>11月6日まで</t>
+          <t>10月28日まで</t>
         </is>
       </c>
     </row>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>セルフプラン件数・相談支援専門員数</t>
+          <t>今期アンケート調査の結果と関係者団体等ヒアリングの結果</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3121,17 +3121,17 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>番号17</t>
+          <t>番号13</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>障がい 第3部第1章⑤・第2章4</t>
+          <t>現状と課題の記述の根拠そのもの</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>骨子の展開まで</t>
+          <t>11月6日まで</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>手帳所持者数の減少要因</t>
+          <t>セルフプラン件数・相談支援専門員数</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3166,17 +3166,17 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>番号24</t>
+          <t>番号17</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>令和5年539人→令和7年508人</t>
+          <t>障がい 第3部第1章⑤・第2章4</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>校了まで</t>
+          <t>骨子の展開まで</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>特別養護老人ホームの入居者数の推移と要因</t>
+          <t>手帳所持者数の減少要因</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3206,22 +3206,22 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>記述</t>
+          <t>障がい</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>番号24</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>収支実績調査票に町のメモがある。事実関係と、計画本文でどこまで書くかを確かめたい</t>
+          <t>令和5年539人→令和7年508人</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>素案の確定まで</t>
+          <t>校了まで</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>計画の策定経過・委員名簿・パブリックコメントの結果</t>
+          <t>特別養護老人ホームの入居者数の推移と要因</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3251,22 +3251,22 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>手続</t>
+          <t>記述</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>番号25</t>
+          <t>―</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>両計画の資料編。【決定後に記載】13箇所</t>
+          <t>収支実績調査票に町のメモがある。事実関係と、計画本文でどこまで書くかを確かめたい</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>校了まで</t>
+          <t>素案の確定まで</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>老人福祉事業の量の目標の前提となる量（養護老人ホーム・軽費老人ホームの本町からの入所者数と老人福祉センターの利用状況）</t>
+          <t>計画の策定経過・委員名簿・パブリックコメントの結果</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3296,22 +3296,22 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>記述</t>
+          <t>手続</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>番号25</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>老人福祉法第20条の8第2項の法定記載事項。介護保険に重ならない3種が素案で未確定（第6章9）</t>
+          <t>両計画の資料編。【決定後に記載】13箇所</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>素案の確定まで</t>
+          <t>校了まで</t>
         </is>
       </c>
     </row>
@@ -3331,32 +3331,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>福島県高齢者居住安定確保計画の改定の予定と内容</t>
+          <t>老人福祉事業の量の目標の前提となる量（養護老人ホーム・軽費老人ホームの本町からの入所者数と老人福祉センターの利用状況）</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>県</t>
+          <t>町</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>整合</t>
+          <t>記述</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Ｄ-6の残り</t>
+          <t>―</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>計画期間が令和8年度で満了し、本計画期間の初日には現行計画が存在しない</t>
+          <t>老人福祉法第20条の8第2項の法定記載事項。介護保険に重ならない3種が素案で未確定（第6章9）</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>最優先</t>
+          <t>素案の確定まで</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>新たな福島県地域医療構想の策定状況</t>
+          <t>福島県高齢者居住安定確保計画の改定の予定と内容</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Ｅ-1</t>
+          <t>Ｄ-6の残り</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>目標年が令和7年。慢性期病床の動きは介護サービス需要に直接効く</t>
+          <t>計画期間が令和8年度で満了し、本計画期間の初日には現行計画が存在しない</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>介護保険法第117条第14項の意見聴取の時期と様式</t>
+          <t>新たな福島県地域医療構想の策定状況</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3431,17 +3431,17 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>手続</t>
+          <t>整合</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Ｋ-3・Ｃ-1</t>
+          <t>Ｅ-1</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>計画を定めるにあたりあらかじめ県の意見を聴かなければならない。中長期推計が対象に加わった</t>
+          <t>目標年が令和7年。慢性期病床の動きは介護サービス需要に直接効く</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>特定地域の省令の基準・県が定める時期・町への意向照会の時期</t>
+          <t>介護保険法第117条第14項の意見聴取の時期と様式</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3476,22 +3476,22 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>特定地域</t>
+          <t>手続</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Ｋ-1・Ｃ-3</t>
+          <t>Ｋ-3・Ｃ-1</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>特定地域サービスの適用</t>
+          <t>計画を定めるにあたりあらかじめ県の意見を聴かなければならない。中長期推計が対象に加わった</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>最優先</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>県中医療圏における精神科医療の体制（にも包括の協議の場の設置状況）</t>
+          <t>特定地域の省令の基準・県が定める時期・町への意向照会の時期</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3521,22 +3521,22 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>障がい</t>
+          <t>特定地域</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Ｆ-1</t>
+          <t>Ｋ-1・Ｃ-3</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>にも包括の成果目標は県が設定し、町は活動指標を置く</t>
+          <t>特定地域サービスの適用</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>最優先</t>
+          <t>高</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>医療的ケア児等支援センターの名称変更・業務の追加と、医療的ケア児等支援地域協議会の設置予定。市町村の「協議の場」の成果目標の扱い</t>
+          <t>県中医療圏における精神科医療の体制（にも包括の協議の場の設置状況）</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -3571,12 +3571,12 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Ｋ-2の残り・Ｆ-2</t>
+          <t>Ｆ-1</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>県保健医療計画より後の改正。コーディネーター配置促進の具体の内容も</t>
+          <t>にも包括の成果目標は県が設定し、町は活動指標を置く</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>調整交付金の算定方法と本町の交付割合の見通し</t>
+          <t>医療的ケア児等支援センターの名称変更・業務の追加と、医療的ケア児等支援地域協議会の設置予定。市町村の「協議の場」の成果目標の扱い</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -3611,22 +3611,22 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>保険料</t>
+          <t>障がい</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Ｃ-2</t>
+          <t>Ｋ-2の残り・Ｆ-2</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>本計画の算定にはこの勘案を織り込んでいない</t>
+          <t>県保健医療計画より後の改正。コーディネーター配置促進の具体の内容も</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>最優先</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>社会福祉法第106条の6の小規模市町村の省令の基準</t>
+          <t>調整交付金の算定方法と本町の交付割合の見通し</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -3656,22 +3656,22 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>整合</t>
+          <t>保険料</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Ｋ-4</t>
+          <t>Ｃ-2</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>該当する場合、両計画の実施体制が変わる</t>
+          <t>本計画の算定にはこの勘案を織り込んでいない</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>夜間対応型訪問介護の経過措置の内容と期間</t>
+          <t>社会福祉法第106条の6の小規模市町村の省令の基準</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -3701,17 +3701,17 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>算定</t>
+          <t>整合</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Ｋ-5・Ｃ-6</t>
+          <t>Ｋ-4</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>本町は0.0人／月のため数値への影響はない。本文の書きぶり</t>
+          <t>該当する場合、両計画の実施体制が変わる</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>第5次福島県障がい者計画の次期計画の策定状況</t>
+          <t>夜間対応型訪問介護の経過措置の内容と期間</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -3746,22 +3746,22 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>障がい</t>
+          <t>算定</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Ｆ-6</t>
+          <t>Ｋ-5・Ｃ-6</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>県障がい者計画は令和9年度で満了する</t>
+          <t>本町は0.0人／月のため数値への影響はない。本文の書きぶり</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
     </row>
@@ -3781,37 +3781,82 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>第5次福島県障がい者計画の次期計画の策定状況</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>県</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>障がい</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Ｆ-6</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>県障がい者計画は令和9年度で満了する</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="54" customHeight="1">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>町の回答・内部データが必要</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
           <t>第10期基本指針（介護）・第8期基本指針の再改正の範囲と時期</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>県</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>整合</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>Ｋ-6・Ｃ-5</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>第10期基本指針は令和9年1月告示の予定</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I74"/>
+  <autoFilter ref="A1:I75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/小野町_引継ぎ_整理済/16_町データ依頼/小野町_確認事項の一覧_20261015.xlsx
+++ b/小野町_引継ぎ_整理済/16_町データ依頼/小野町_確認事項の一覧_20261015.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="確認事項の一覧" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'確認事項の一覧'!$A$1:$I$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'確認事項の一覧'!$A$1:$I$77</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>計画の策定経過・委員名簿・パブリックコメントの結果</t>
+          <t>前回計画 第7期の短期入所の見込量の置き方（実績のある福祉型を0とし、実績のない医療型に見込みを立てている）</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3296,22 +3296,22 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>手続</t>
+          <t>障がい</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>番号25</t>
+          <t>―</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>両計画の資料編。【決定後に記載】13箇所</t>
+          <t>第8期の見込量に引き継いではならない。本文は「各年度3人、24人日」とするが表は2人で、24÷12＝2人とも合わない</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>校了まで</t>
+          <t>素案の確定まで</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>老人福祉事業の量の目標の前提となる量（養護老人ホーム・軽費老人ホームの本町からの入所者数と老人福祉センターの利用状況）</t>
+          <t>前回計画 第7期（障がい児）の人と人日の入れ替わり（児童発達支援38人・4人日／放課後等デイ391人・23人日）</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>記述</t>
+          <t>障がい</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>老人福祉法第20条の8第2項の法定記載事項。介護保険に重ならない3種が素案で未確定（第6章9）</t>
+          <t>手帳所持者508人の町で放課後等デイを月391人が利用することはありえない。第6期の実績は31人・93人日</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3376,32 +3376,32 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>福島県高齢者居住安定確保計画の改定の予定と内容</t>
+          <t>計画の策定経過・委員名簿・パブリックコメントの結果</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>県</t>
+          <t>町</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>整合</t>
+          <t>手続</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Ｄ-6の残り</t>
+          <t>番号25</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>計画期間が令和8年度で満了し、本計画期間の初日には現行計画が存在しない</t>
+          <t>両計画の資料編。【決定後に記載】13箇所</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>最優先</t>
+          <t>校了まで</t>
         </is>
       </c>
     </row>
@@ -3421,32 +3421,32 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>新たな福島県地域医療構想の策定状況</t>
+          <t>老人福祉事業の量の目標の前提となる量（養護老人ホーム・軽費老人ホームの本町からの入所者数と老人福祉センターの利用状況）</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>県</t>
+          <t>町</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>整合</t>
+          <t>記述</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Ｅ-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>目標年が令和7年。慢性期病床の動きは介護サービス需要に直接効く</t>
+          <t>老人福祉法第20条の8第2項の法定記載事項。介護保険に重ならない3種が素案で未確定（第6章9）</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>最優先</t>
+          <t>素案の確定まで</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>介護保険法第117条第14項の意見聴取の時期と様式</t>
+          <t>福島県高齢者居住安定確保計画の改定の予定と内容</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3476,17 +3476,17 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>手続</t>
+          <t>整合</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Ｋ-3・Ｃ-1</t>
+          <t>Ｄ-6の残り</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>計画を定めるにあたりあらかじめ県の意見を聴かなければならない。中長期推計が対象に加わった</t>
+          <t>計画期間が令和8年度で満了し、本計画期間の初日には現行計画が存在しない</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>特定地域の省令の基準・県が定める時期・町への意向照会の時期</t>
+          <t>新たな福島県地域医療構想の策定状況</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3521,22 +3521,22 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>特定地域</t>
+          <t>整合</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Ｋ-1・Ｃ-3</t>
+          <t>Ｅ-1</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>特定地域サービスの適用</t>
+          <t>目標年が令和7年。慢性期病床の動きは介護サービス需要に直接効く</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>最優先</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>県中医療圏における精神科医療の体制（にも包括の協議の場の設置状況）</t>
+          <t>介護保険法第117条第14項の意見聴取の時期と様式</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>障がい</t>
+          <t>手続</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Ｆ-1</t>
+          <t>Ｋ-3・Ｃ-1</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>にも包括の成果目標は県が設定し、町は活動指標を置く</t>
+          <t>計画を定めるにあたりあらかじめ県の意見を聴かなければならない。中長期推計が対象に加わった</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>医療的ケア児等支援センターの名称変更・業務の追加と、医療的ケア児等支援地域協議会の設置予定。市町村の「協議の場」の成果目標の扱い</t>
+          <t>特定地域の省令の基準・県が定める時期・町への意向照会の時期</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -3611,22 +3611,22 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>障がい</t>
+          <t>特定地域</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Ｋ-2の残り・Ｆ-2</t>
+          <t>Ｋ-1・Ｃ-3</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>県保健医療計画より後の改正。コーディネーター配置促進の具体の内容も</t>
+          <t>特定地域サービスの適用</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>最優先</t>
+          <t>高</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>調整交付金の算定方法と本町の交付割合の見通し</t>
+          <t>県中医療圏における精神科医療の体制（にも包括の協議の場の設置状況）</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -3656,22 +3656,22 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>保険料</t>
+          <t>障がい</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Ｃ-2</t>
+          <t>Ｆ-1</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>本計画の算定にはこの勘案を織り込んでいない</t>
+          <t>にも包括の成果目標は県が設定し、町は活動指標を置く</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>最優先</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>社会福祉法第106条の6の小規模市町村の省令の基準</t>
+          <t>医療的ケア児等支援センターの名称変更・業務の追加と、医療的ケア児等支援地域協議会の設置予定。市町村の「協議の場」の成果目標の扱い</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -3701,22 +3701,22 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>整合</t>
+          <t>障がい</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Ｋ-4</t>
+          <t>Ｋ-2の残り・Ｆ-2</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>該当する場合、両計画の実施体制が変わる</t>
+          <t>県保健医療計画より後の改正。コーディネーター配置促進の具体の内容も</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>最優先</t>
         </is>
       </c>
     </row>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>夜間対応型訪問介護の経過措置の内容と期間</t>
+          <t>調整交付金の算定方法と本町の交付割合の見通し</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -3746,22 +3746,22 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>算定</t>
+          <t>保険料</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Ｋ-5・Ｃ-6</t>
+          <t>Ｃ-2</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>本町は0.0人／月のため数値への影響はない。本文の書きぶり</t>
+          <t>本計画の算定にはこの勘案を織り込んでいない</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>第5次福島県障がい者計画の次期計画の策定状況</t>
+          <t>社会福祉法第106条の6の小規模市町村の省令の基準</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -3791,22 +3791,22 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>障がい</t>
+          <t>整合</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Ｆ-6</t>
+          <t>Ｋ-4</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>県障がい者計画は令和9年度で満了する</t>
+          <t>該当する場合、両計画の実施体制が変わる</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
     </row>
@@ -3826,37 +3826,127 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>夜間対応型訪問介護の経過措置の内容と期間</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>県</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>算定</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Ｋ-5・Ｃ-6</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>本町は0.0人／月のため数値への影響はない。本文の書きぶり</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="54" customHeight="1">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>町の回答・内部データが必要</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>第5次福島県障がい者計画の次期計画の策定状況</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>県</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>障がい</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Ｆ-6</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>県障がい者計画は令和9年度で満了する</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="54" customHeight="1">
+      <c r="A77" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>町の回答・内部データが必要</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
           <t>第10期基本指針（介護）・第8期基本指針の再改正の範囲と時期</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>県</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>整合</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>Ｋ-6・Ｃ-5</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>第10期基本指針は令和9年1月告示の予定</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I75"/>
+  <autoFilter ref="A1:I77"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/小野町_引継ぎ_整理済/16_町データ依頼/小野町_確認事項の一覧_20261015.xlsx
+++ b/小野町_引継ぎ_整理済/16_町データ依頼/小野町_確認事項の一覧_20261015.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="確認事項の一覧" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'確認事項の一覧'!$A$1:$I$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'確認事項の一覧'!$A$1:$I$79</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>前回計画 第7期の短期入所の見込量の置き方（実績のある福祉型を0とし、実績のない医療型に見込みを立てている）</t>
+          <t>地域生活支援事業4事業の実績が0である理由（意思疎通支援・手話奉仕員養成・移動支援・地域活動支援センター）</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>第8期の見込量に引き継いではならない。本文は「各年度3人、24人日」とするが表は2人で、24÷12＝2人とも合わない</t>
+          <t>前回計画は第6期の実績も第7期の見込量もすべて0。必要がなかったのか、使える形になっていなかったのかで、本計画ですべきことが正反対になる。令和7年4月に手話言語条例を施行している</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>素案の確定まで</t>
+          <t>最優先</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>前回計画 第7期（障がい児）の人と人日の入れ替わり（児童発達支援38人・4人日／放課後等デイ391人・23人日）</t>
+          <t>前回計画 第7期の成果目標①（施設入所者の地域生活移行）の由来（入所者26人に対し移行31人・削減22人）</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>手帳所持者508人の町で放課後等デイを月391人が利用することはありえない。第6期の実績は31人・93人日</t>
+          <t>入所者より多い人数が移行することはできない。削減22人なら残り4人だが、同じ計画の見込量は施設入所支援15人。国の指針を26人に当てはめると移行2人・削減2人</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>計画の策定経過・委員名簿・パブリックコメントの結果</t>
+          <t>前回計画 第7期の短期入所の見込量の置き方（実績のある福祉型を0とし、実績のない医療型に見込みを立てている）</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3386,22 +3386,22 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>手続</t>
+          <t>障がい</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>番号25</t>
+          <t>―</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>両計画の資料編。【決定後に記載】13箇所</t>
+          <t>第8期の見込量に引き継いではならない。本文は「各年度3人、24人日」とするが表は2人で、24÷12＝2人とも合わない</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>校了まで</t>
+          <t>素案の確定まで</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>老人福祉事業の量の目標の前提となる量（養護老人ホーム・軽費老人ホームの本町からの入所者数と老人福祉センターの利用状況）</t>
+          <t>前回計画 第7期（障がい児）の人と人日の入れ替わり（児童発達支援38人・4人日／放課後等デイ391人・23人日）</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>記述</t>
+          <t>障がい</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>老人福祉法第20条の8第2項の法定記載事項。介護保険に重ならない3種が素案で未確定（第6章9）</t>
+          <t>手帳所持者508人の町で放課後等デイを月391人が利用することはありえない。第6期の実績は31人・93人日</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -3466,32 +3466,32 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>福島県高齢者居住安定確保計画の改定の予定と内容</t>
+          <t>計画の策定経過・委員名簿・パブリックコメントの結果</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>県</t>
+          <t>町</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>整合</t>
+          <t>手続</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Ｄ-6の残り</t>
+          <t>番号25</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>計画期間が令和8年度で満了し、本計画期間の初日には現行計画が存在しない</t>
+          <t>両計画の資料編。【決定後に記載】13箇所</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>最優先</t>
+          <t>校了まで</t>
         </is>
       </c>
     </row>
@@ -3511,32 +3511,32 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>新たな福島県地域医療構想の策定状況</t>
+          <t>老人福祉事業の量の目標の前提となる量（養護老人ホーム・軽費老人ホームの本町からの入所者数と老人福祉センターの利用状況）</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>県</t>
+          <t>町</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>整合</t>
+          <t>記述</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Ｅ-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>目標年が令和7年。慢性期病床の動きは介護サービス需要に直接効く</t>
+          <t>老人福祉法第20条の8第2項の法定記載事項。介護保険に重ならない3種が素案で未確定（第6章9）</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>最優先</t>
+          <t>素案の確定まで</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>介護保険法第117条第14項の意見聴取の時期と様式</t>
+          <t>福島県高齢者居住安定確保計画の改定の予定と内容</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>手続</t>
+          <t>整合</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Ｋ-3・Ｃ-1</t>
+          <t>Ｄ-6の残り</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>計画を定めるにあたりあらかじめ県の意見を聴かなければならない。中長期推計が対象に加わった</t>
+          <t>計画期間が令和8年度で満了し、本計画期間の初日には現行計画が存在しない</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>特定地域の省令の基準・県が定める時期・町への意向照会の時期</t>
+          <t>新たな福島県地域医療構想の策定状況</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -3611,22 +3611,22 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>特定地域</t>
+          <t>整合</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Ｋ-1・Ｃ-3</t>
+          <t>Ｅ-1</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>特定地域サービスの適用</t>
+          <t>目標年が令和7年。慢性期病床の動きは介護サービス需要に直接効く</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>最優先</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>県中医療圏における精神科医療の体制（にも包括の協議の場の設置状況）</t>
+          <t>介護保険法第117条第14項の意見聴取の時期と様式</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -3656,17 +3656,17 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>障がい</t>
+          <t>手続</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Ｆ-1</t>
+          <t>Ｋ-3・Ｃ-1</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>にも包括の成果目標は県が設定し、町は活動指標を置く</t>
+          <t>計画を定めるにあたりあらかじめ県の意見を聴かなければならない。中長期推計が対象に加わった</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>医療的ケア児等支援センターの名称変更・業務の追加と、医療的ケア児等支援地域協議会の設置予定。市町村の「協議の場」の成果目標の扱い</t>
+          <t>特定地域の省令の基準・県が定める時期・町への意向照会の時期</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -3701,22 +3701,22 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>障がい</t>
+          <t>特定地域</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Ｋ-2の残り・Ｆ-2</t>
+          <t>Ｋ-1・Ｃ-3</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>県保健医療計画より後の改正。コーディネーター配置促進の具体の内容も</t>
+          <t>特定地域サービスの適用</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>最優先</t>
+          <t>高</t>
         </is>
       </c>
     </row>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>調整交付金の算定方法と本町の交付割合の見通し</t>
+          <t>県中医療圏における精神科医療の体制（にも包括の協議の場の設置状況）</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -3746,22 +3746,22 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>保険料</t>
+          <t>障がい</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Ｃ-2</t>
+          <t>Ｆ-1</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>本計画の算定にはこの勘案を織り込んでいない</t>
+          <t>にも包括の成果目標は県が設定し、町は活動指標を置く</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>最優先</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>社会福祉法第106条の6の小規模市町村の省令の基準</t>
+          <t>医療的ケア児等支援センターの名称変更・業務の追加と、医療的ケア児等支援地域協議会の設置予定。市町村の「協議の場」の成果目標の扱い</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -3791,22 +3791,22 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>整合</t>
+          <t>障がい</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Ｋ-4</t>
+          <t>Ｋ-2の残り・Ｆ-2</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>該当する場合、両計画の実施体制が変わる</t>
+          <t>県保健医療計画より後の改正。コーディネーター配置促進の具体の内容も</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>最優先</t>
         </is>
       </c>
     </row>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>夜間対応型訪問介護の経過措置の内容と期間</t>
+          <t>調整交付金の算定方法と本町の交付割合の見通し</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -3836,22 +3836,22 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>算定</t>
+          <t>保険料</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Ｋ-5・Ｃ-6</t>
+          <t>Ｃ-2</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>本町は0.0人／月のため数値への影響はない。本文の書きぶり</t>
+          <t>本計画の算定にはこの勘案を織り込んでいない</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
     </row>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>第5次福島県障がい者計画の次期計画の策定状況</t>
+          <t>社会福祉法第106条の6の小規模市町村の省令の基準</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -3881,22 +3881,22 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>障がい</t>
+          <t>整合</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Ｆ-6</t>
+          <t>Ｋ-4</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>県障がい者計画は令和9年度で満了する</t>
+          <t>該当する場合、両計画の実施体制が変わる</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
     </row>
@@ -3916,37 +3916,127 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
+          <t>夜間対応型訪問介護の経過措置の内容と期間</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>県</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>算定</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Ｋ-5・Ｃ-6</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>本町は0.0人／月のため数値への影響はない。本文の書きぶり</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="54" customHeight="1">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>町の回答・内部データが必要</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>第5次福島県障がい者計画の次期計画の策定状況</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>県</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>障がい</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Ｆ-6</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>県障がい者計画は令和9年度で満了する</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="54" customHeight="1">
+      <c r="A79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>町の回答・内部データが必要</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
           <t>第10期基本指針（介護）・第8期基本指針の再改正の範囲と時期</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>県</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>整合</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>Ｋ-6・Ｃ-5</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>第10期基本指針は令和9年1月告示の予定</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I77"/>
+  <autoFilter ref="A1:I79"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/小野町_引継ぎ_整理済/16_町データ依頼/小野町_確認事項の一覧_20261015.xlsx
+++ b/小野町_引継ぎ_整理済/16_町データ依頼/小野町_確認事項の一覧_20261015.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="確認事項の一覧" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'確認事項の一覧'!$A$1:$I$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'確認事項の一覧'!$A$1:$I$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>地域生活支援事業4事業の実績が0である理由（意思疎通支援・手話奉仕員養成・移動支援・地域活動支援センター）</t>
+          <t>前回計画 第2部（障がい者計画）49項目・96取組の実績</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>前回計画は第6期の実績も第7期の見込量もすべて0。必要がなかったのか、使える形になっていなかったのかで、本計画ですべきことが正反対になる。令和7年4月に手話言語条例を施行している</t>
+          <t>分野別施策の取組状況（素案 第1部第3章3）。前回計画が掲げた取組が、どこまで行われたか。9分野すべてを引き継ぐため、分野ごとに要る</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>最優先</t>
+          <t>素案の確定まで</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>前回計画 第7期の成果目標①（施設入所者の地域生活移行）の由来（入所者26人に対し移行31人・削減22人）</t>
+          <t>地域生活支援事業4事業の実績が0である理由（意思疎通支援・手話奉仕員養成・移動支援・地域活動支援センター）</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>入所者より多い人数が移行することはできない。削減22人なら残り4人だが、同じ計画の見込量は施設入所支援15人。国の指針を26人に当てはめると移行2人・削減2人</t>
+          <t>前回計画は第6期の実績も第7期の見込量もすべて0。必要がなかったのか、使える形になっていなかったのかで、本計画ですべきことが正反対になる。令和7年4月に手話言語条例を施行している</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>素案の確定まで</t>
+          <t>最優先</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>前回計画 第7期の短期入所の見込量の置き方（実績のある福祉型を0とし、実績のない医療型に見込みを立てている）</t>
+          <t>前回計画 第7期の成果目標①（施設入所者の地域生活移行）の由来（入所者26人に対し移行31人・削減22人）</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>第8期の見込量に引き継いではならない。本文は「各年度3人、24人日」とするが表は2人で、24÷12＝2人とも合わない</t>
+          <t>入所者より多い人数が移行することはできない。削減22人なら残り4人だが、同じ計画の見込量は施設入所支援15人。国の指針を26人に当てはめると移行2人・削減2人</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>前回計画 第7期（障がい児）の人と人日の入れ替わり（児童発達支援38人・4人日／放課後等デイ391人・23人日）</t>
+          <t>前回計画 第7期の短期入所の見込量の置き方（実績のある福祉型を0とし、実績のない医療型に見込みを立てている）</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>手帳所持者508人の町で放課後等デイを月391人が利用することはありえない。第6期の実績は31人・93人日</t>
+          <t>第8期の見込量に引き継いではならない。本文は「各年度3人、24人日」とするが表は2人で、24÷12＝2人とも合わない</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>計画の策定経過・委員名簿・パブリックコメントの結果</t>
+          <t>前回計画 第7期（障がい児）の人と人日の入れ替わり（児童発達支援38人・4人日／放課後等デイ391人・23人日）</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3476,22 +3476,22 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>手続</t>
+          <t>障がい</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>番号25</t>
+          <t>―</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>両計画の資料編。【決定後に記載】13箇所</t>
+          <t>手帳所持者508人の町で放課後等デイを月391人が利用することはありえない。第6期の実績は31人・93人日</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>校了まで</t>
+          <t>素案の確定まで</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>老人福祉事業の量の目標の前提となる量（養護老人ホーム・軽費老人ホームの本町からの入所者数と老人福祉センターの利用状況）</t>
+          <t>計画の策定経過・委員名簿・パブリックコメントの結果</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3521,22 +3521,22 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>記述</t>
+          <t>手続</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>番号25</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>老人福祉法第20条の8第2項の法定記載事項。介護保険に重ならない3種が素案で未確定（第6章9）</t>
+          <t>両計画の資料編。【決定後に記載】13箇所</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>素案の確定まで</t>
+          <t>校了まで</t>
         </is>
       </c>
     </row>
@@ -3556,32 +3556,32 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>福島県高齢者居住安定確保計画の改定の予定と内容</t>
+          <t>老人福祉事業の量の目標の前提となる量（養護老人ホーム・軽費老人ホームの本町からの入所者数と老人福祉センターの利用状況）</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>県</t>
+          <t>町</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>整合</t>
+          <t>記述</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Ｄ-6の残り</t>
+          <t>―</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>計画期間が令和8年度で満了し、本計画期間の初日には現行計画が存在しない</t>
+          <t>老人福祉法第20条の8第2項の法定記載事項。介護保険に重ならない3種が素案で未確定（第6章9）</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>最優先</t>
+          <t>素案の確定まで</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>新たな福島県地域医療構想の策定状況</t>
+          <t>福島県高齢者居住安定確保計画の改定の予定と内容</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Ｅ-1</t>
+          <t>Ｄ-6の残り</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>目標年が令和7年。慢性期病床の動きは介護サービス需要に直接効く</t>
+          <t>計画期間が令和8年度で満了し、本計画期間の初日には現行計画が存在しない</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>介護保険法第117条第14項の意見聴取の時期と様式</t>
+          <t>新たな福島県地域医療構想の策定状況</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -3656,17 +3656,17 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>手続</t>
+          <t>整合</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Ｋ-3・Ｃ-1</t>
+          <t>Ｅ-1</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>計画を定めるにあたりあらかじめ県の意見を聴かなければならない。中長期推計が対象に加わった</t>
+          <t>目標年が令和7年。慢性期病床の動きは介護サービス需要に直接効く</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>特定地域の省令の基準・県が定める時期・町への意向照会の時期</t>
+          <t>介護保険法第117条第14項の意見聴取の時期と様式</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -3701,22 +3701,22 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>特定地域</t>
+          <t>手続</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Ｋ-1・Ｃ-3</t>
+          <t>Ｋ-3・Ｃ-1</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>特定地域サービスの適用</t>
+          <t>計画を定めるにあたりあらかじめ県の意見を聴かなければならない。中長期推計が対象に加わった</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>最優先</t>
         </is>
       </c>
     </row>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>県中医療圏における精神科医療の体制（にも包括の協議の場の設置状況）</t>
+          <t>特定地域の省令の基準・県が定める時期・町への意向照会の時期</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -3746,22 +3746,22 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>障がい</t>
+          <t>特定地域</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Ｆ-1</t>
+          <t>Ｋ-1・Ｃ-3</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>にも包括の成果目標は県が設定し、町は活動指標を置く</t>
+          <t>特定地域サービスの適用</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>最優先</t>
+          <t>高</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>医療的ケア児等支援センターの名称変更・業務の追加と、医療的ケア児等支援地域協議会の設置予定。市町村の「協議の場」の成果目標の扱い</t>
+          <t>県中医療圏における精神科医療の体制（にも包括の協議の場の設置状況）</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Ｋ-2の残り・Ｆ-2</t>
+          <t>Ｆ-1</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>県保健医療計画より後の改正。コーディネーター配置促進の具体の内容も</t>
+          <t>にも包括の成果目標は県が設定し、町は活動指標を置く</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>調整交付金の算定方法と本町の交付割合の見通し</t>
+          <t>医療的ケア児等支援センターの名称変更・業務の追加と、医療的ケア児等支援地域協議会の設置予定。市町村の「協議の場」の成果目標の扱い</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -3836,22 +3836,22 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>保険料</t>
+          <t>障がい</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Ｃ-2</t>
+          <t>Ｋ-2の残り・Ｆ-2</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>本計画の算定にはこの勘案を織り込んでいない</t>
+          <t>県保健医療計画より後の改正。コーディネーター配置促進の具体の内容も</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>最優先</t>
         </is>
       </c>
     </row>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>社会福祉法第106条の6の小規模市町村の省令の基準</t>
+          <t>調整交付金の算定方法と本町の交付割合の見通し</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -3881,22 +3881,22 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>整合</t>
+          <t>保険料</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Ｋ-4</t>
+          <t>Ｃ-2</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>該当する場合、両計画の実施体制が変わる</t>
+          <t>本計画の算定にはこの勘案を織り込んでいない</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
     </row>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>夜間対応型訪問介護の経過措置の内容と期間</t>
+          <t>社会福祉法第106条の6の小規模市町村の省令の基準</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -3926,17 +3926,17 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>算定</t>
+          <t>整合</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Ｋ-5・Ｃ-6</t>
+          <t>Ｋ-4</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>本町は0.0人／月のため数値への影響はない。本文の書きぶり</t>
+          <t>該当する場合、両計画の実施体制が変わる</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>第5次福島県障がい者計画の次期計画の策定状況</t>
+          <t>夜間対応型訪問介護の経過措置の内容と期間</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -3971,22 +3971,22 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>障がい</t>
+          <t>算定</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Ｆ-6</t>
+          <t>Ｋ-5・Ｃ-6</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>県障がい者計画は令和9年度で満了する</t>
+          <t>本町は0.0人／月のため数値への影響はない。本文の書きぶり</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
     </row>
@@ -4006,37 +4006,82 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
+          <t>第5次福島県障がい者計画の次期計画の策定状況</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>県</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>障がい</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Ｆ-6</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>県障がい者計画は令和9年度で満了する</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="54" customHeight="1">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>町の回答・内部データが必要</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
           <t>第10期基本指針（介護）・第8期基本指針の再改正の範囲と時期</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>県</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>整合</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>Ｋ-6・Ｃ-5</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>第10期基本指針は令和9年1月告示の予定</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I79"/>
+  <autoFilter ref="A1:I80"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/小野町_引継ぎ_整理済/16_町データ依頼/小野町_確認事項の一覧_20261015.xlsx
+++ b/小野町_引継ぎ_整理済/16_町データ依頼/小野町_確認事項の一覧_20261015.xlsx
@@ -1069,19 +1069,19 @@
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Ｂ</t>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Ａ</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>当方で一次資料を確認</t>
+          <t>解決済み</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>介護保険法第117条の改正後の項番号（医療計画との整合、地域福祉計画等との調和）</t>
+          <t>介護保険法第117条の項番号（整合性の確保・調和・一体作成）</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>第2項の号（施策=第5号・目標=第6号）と項の繰り下がりは条文で確定（内部検討7-1・7-2）。残るのは医療計画との整合・老人福祉計画との一体・地域福祉計画等との調和がどの項かで、現行条文の全文が要る。素案は項番号を書いていないため支障はない</t>
+          <t>現行条文で確定。 現行14項・改正後15項。整合性の確保＝第10項（改正後第11項。相手方は医療介護総合確保促進法第5条第1項の市町村計画であり、医療計画ではない）、調和＝第11項（改正後第12項）、老人福祉計画との一体＝第7項（改正後第8項）</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>素案の確定まで</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -1114,14 +1114,14 @@
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Ｂ</t>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Ａ</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>当方で一次資料を確認</t>
+          <t>解決済み</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>検索結果によるものであり、原典で確かめてから本文に書く</t>
+          <t>現行条文で確定。 市町村高齢者居住安定確保計画＝高齢者住まい法第4条の2、市町村賃貸住宅供給促進計画＝住宅セーフティネット法第6条、居住支援協議会＝同法第81条、登録住宅＝高齢者住まい法第7条第5項。いずれも当方の記載どおり</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>素案の確定まで</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -1159,14 +1159,14 @@
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Ｂ</t>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Ａ</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>当方で一次資料を確認</t>
+          <t>解決済み</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>第88条・第33条の20はどちらも新旧とも12項で、項・号の繰り下がりがないことを条文で確定（内部検討8）。現行条文で確かめた番号をそのまま計画期間中使える。調和の規定の番号自体は未確認</t>
+          <t>現行条文で確定。調和＝第88条第7項・第33条の20第7項（当方は第5項としていた。訂正済み）。一体作成＝いずれも第6項。協議会の意見聴取＝いずれも第9項。どちらも全12項で繰り下がりなし</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>骨子の展開まで</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -1204,19 +1204,19 @@
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Ｂ</t>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Ａ</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>当方で一次資料を確認</t>
+          <t>解決済み</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>特別地域加算の対象地域の現行の大臣告示</t>
+          <t>手話に関する施策の推進に関する法律の法律番号と施行日</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1226,22 +1226,22 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>特定地域</t>
+          <t>法令</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Ｋ-1の一部</t>
+          <t>―</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>ご提供の一覧は平成30年4月時点の民間団体の整理。現行の告示（平成12年厚生省告示第24号の最新改正）で確かめる</t>
+          <t>法令APIで確定。令和7年法律第78号、公布 令和7年6月25日、施行は公布の日（附則第1項）。第3条が国及び地方公共団体の責務を定める</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>素案の確定まで</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>農林水産省「振興山村一覧表」</t>
+          <t>特別地域加算の対象地域の現行の大臣告示</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>Ｋ-1の一部</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>検索結果により小野町 旧夏井村・指定番号1179を確かめたにとどまる。一覧の現物で確かめる</t>
+          <t>ご提供の一覧は平成30年4月時点の民間団体の整理。現行の告示（平成12年厚生省告示第24号の最新改正）で確かめる</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>手話に関する施策の推進に関する法律の法律番号と施行日</t>
+          <t>農林水産省「振興山村一覧表」</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>法令</t>
+          <t>特定地域</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>障がい素案 第2部第4章の根拠。令和7年6月成立までは確かめたが、法律番号が未確認。町条例（令和7年4月）とあわせて書く</t>
+          <t>検索結果により小野町 旧夏井村・指定番号1179を確かめたにとどまる。一覧の現物で確かめる</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>骨子の展開まで</t>
+          <t>素案の確定まで</t>
         </is>
       </c>
     </row>
@@ -1951,17 +1951,17 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Ｈ-1・Ａ-3</t>
+          <t>Ｃ-4</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>法定の勘案事項（介保法第117条第5項第1号）。県高齢者居住安定確保計画の【基本事項】②でも市町村に求められている。該当なしの確認でもよい</t>
+          <t>介護保険法第117条第5項【新設】の勘案事項。高齢者住まい法第7条第5項により、県知事はサ高住の登録をしたとき市町村長に通知しなければならない。町に通知が届いているはず。第9期計画は「設置状況の把握に努めます」としており、改正で勘案義務になった</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>11月6日まで</t>
+          <t>最優先</t>
         </is>
       </c>
     </row>

--- a/小野町_引継ぎ_整理済/16_町データ依頼/小野町_確認事項の一覧_20261015.xlsx
+++ b/小野町_引継ぎ_整理済/16_町データ依頼/小野町_確認事項の一覧_20261015.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="確認事項の一覧" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'確認事項の一覧'!$A$1:$I$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'確認事項の一覧'!$A$1:$I$84</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I80"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>計画の策定手続そのもの。設置していれば策定・変更にあたり意見を聴くよう努めなければならない</t>
+          <t>計画の策定手続そのもの。設置していれば策定・変更にあたり意見を聴くよう努めなければならない。あわせて、社会福祉法第106条の3の2の支援会議、住宅セーフティネット法第81条第1項の居住支援協議会、生活困窮者自立支援法第9条第1項の支援会議の設置の有無も。改正後の介護保険法第115条の48第5項は、これら5つとの相互の連携を努力義務としている</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>医療的ケア児等の人数と状況（18歳以上の医療的ケア者・重症心身障害者を含む）と個別避難計画の作成状況</t>
+          <t>医療的ケア児等の人数と状況（18歳以上の医療的ケア児等・重症心身障害者を含む）と個別避難計画の作成状況</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>特定地域サービスの適用</t>
+          <t>特定地域を定めるのは県である（介護保険法第42条第1項第3号。改正後条文で確定）。 基準は厚生労働省令だが、令和8年10月19日現在、公布されていない（介護保険法施行規則・同法施行令の令和9年4月1日時点の版を法令APIで確認。「特定地域」の語を含む条はない）。本町が定められた場合、特定地域居宅サービス等事業の費用が第2号被保険者の負担の対象に入るため、保険料の算定をやり直す</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>該当する場合、両計画の実施体制が変わる</t>
+          <t>条文は「その人口規模、その人口の減少の状況等からみて福祉サービスを提供する体制の確保に支障を生じ、又は生ずるおそれがあると認められる市町村として厚生労働省令で定める基準に該当するもの」とのみ定める（改正後条文で確定）。 具体の指標は省令次第であり、その省令は令和8年10月19日現在、公布されていない（社会福祉法施行規則を法令APIで確認）。該当する場合、地域包括支援センターの3事業と生活支援体制整備事業を障がい・子ども・生活困窮の各事業と一体に実施することになり、両計画の実施体制が変わる。従事職員・員数の基準も省令</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -4080,8 +4080,188 @@
         </is>
       </c>
     </row>
+    <row r="81" ht="54" customHeight="1">
+      <c r="A81" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>Ａ</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>解決済み</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>特定地域居宅サービス等事業の根拠・対象サービス・費用の扱い</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>特定地域</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>改正後条文で確定（法令API v2・asof 令和9年4月1日）。根拠＝介護保険法第115条の45第3項【新設】。対象＝要介護者に訪問介護・訪問入浴介護・通所介護・短期入所生活介護、要支援者に介護予防訪問入浴介護・介護予防短期入所生活介護。特定地域＝「人口の減少その他の厚生労働省令で定める基準に該当する地域として都道府県が定めるもの」（同法第42条第1項第3号）。費用は総合事業と同じく第2号被保険者の負担の対象（第126条第1項）、国の「特定地域支援事業支援額」からは除外（第122条の2第4項）。この新設により同条の項が1つずつ繰り下がり、任意事業は第4項になる</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="54" customHeight="1">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Ａ</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>解決済み</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>小規模市町村地域支援連携協働体制整備事業の根拠と一体実施の対象</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>整合</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>改正後条文で確定（法令API v2・asof 令和9年4月1日）。根拠＝社会福祉法第106条の6【丸ごと差し替え】。小規模市町村＝「その人口規模、その人口の減少の状況等からみて福祉サービスを提供する体制の確保に支障を生じ、又は生ずるおそれがあると認められる市町村として厚生労働省令で定める基準に該当するもの」。一体に行う事業は、相談＝介護保険法第115条の45第2項第1号〜第3号（地域包括支援センターの3事業）・障害者総合支援法第77条第1項第3号・子ども子育て支援法第59条第1号・生活困窮者自立支援法第3条第2項各号、地域づくり＝介護保険法第115条の45第1項第2号の一部及び同条第2項第5号（生活支援体制整備事業）ほか。実施は任意（「行うことができる」）</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="54" customHeight="1">
+      <c r="A83" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>Ａ</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>解決済み</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>支援会議の相互連携の相手方（2つではなく5つ）</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>手続</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>改正後条文で確定。介護保険法第115条の48第5項【新設】は、障害者総合支援法第89条の3第1項の支援協議会のほか、社会福祉法第106条の3の2第1項の支援会議・住宅セーフティネット法第81条第1項の支援協議会・生活困窮者自立支援法第9条第1項の支援会議その他の会議を挙げる。障害者総合支援法第89条の3第5項も同じ構成。介護保険法第115条の48は全6項→全9項（第6項＝地域包括支援センターの設置者への委託、第7項＝包括的支援事業との連携と住民の意見の反映）</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="54" customHeight="1">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Ａ</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>解決済み</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>老人福祉法第20条の8の改正の有無</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>法令</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>改正後条文で確定。当方は「改正の対象外」としていたが誤り（訂正済み）。 量の目標を定める第2項は改正されないが、第3項に第3号が新設される（老人福祉事業等を営む者と社会福祉法第4条第3項の支援関係機関との連携に関する事項。努力義務）。令和9年4月1日施行</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I80"/>
+  <autoFilter ref="A1:I84"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/小野町_引継ぎ_整理済/16_町データ依頼/小野町_確認事項の一覧_20261015.xlsx
+++ b/小野町_引継ぎ_整理済/16_町データ依頼/小野町_確認事項の一覧_20261015.xlsx
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>ご提供の一覧は平成30年4月時点の民間団体の整理。現行の告示（平成12年厚生省告示第24号の最新改正）で確かめる</t>
+          <t>ご提供の一覧は平成30年4月時点の民間団体の整理。現行の告示（平成12年厚生省告示第24号の最新改正）で確かめる。法令API（e-Gov）は法律・政令・省令を返すが、告示は対象外であることを令和8年10月19日に確かめた（法令種別に「告示」がなく、題名で探しても0件）。官報又は厚生労働省の公表による</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>保険料の最大の論点。取崩しなし6,053円／12,000千円で6,000円弱／35,000千円で5,808円。取崩しが7年間0であったと分かり、残高が想定より大きい可能性がある</t>
+          <t>保険料の最大の論点。町の財務書類で令和5年度末120,000千円、令和8年度末見込210,000千円。取崩しなし6,053円／105,000千円（令和8年度末見込の半分）で5,194円／210,000千円（全額）で4,334円。残るのは令和7年度末の残高（財産に関する調書）の確認</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">

--- a/小野町_引継ぎ_整理済/16_町データ依頼/小野町_確認事項の一覧_20261015.xlsx
+++ b/小野町_引継ぎ_整理済/16_町データ依頼/小野町_確認事項の一覧_20261015.xlsx
@@ -1056,7 +1056,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>見える化Ｄ25 で確定。本町に介護医療院はない（平成27〜令和7年度すべて「−」）。県の表の介護医療院58人は、地域密着型介護老人福祉施設の定員が1行下にずれたもの。素案 第2章5 は訂正不要</t>
+          <t>見える化Ｄ25 で確定。本町に介護医療院はない（平成27〜令和7年度すべて「−」）。県の表の介護医療院58人は、地域密着型介護老人福祉施設の定員が1行下にずれたもの。素案 第2章5 は変更は要らない</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>現行条文で確定。調和＝第88条第7項・第33条の20第7項（当方は第5項としていた。訂正済み）。一体作成＝いずれも第6項。協議会の意見聴取＝いずれも第9項。どちらも全12項で繰り下がりなし</t>
+          <t>現行条文で確定。調和＝第88条第7項・第33条の20第7項。一体作成＝いずれも第6項。協議会の意見聴取＝いずれも第9項。どちらも全12項で繰り下がりなし</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>改正後条文で確定。当方は「改正の対象外」としていたが誤り（訂正済み）。 量の目標を定める第2項は改正されないが、第3項に第3号が新設される（老人福祉事業等を営む者と社会福祉法第4条第3項の支援関係機関との連携に関する事項。努力義務）。令和9年4月1日施行</t>
+          <t>改正後条文で確定。 量の目標を定める第2項は改正されないが、第3項に第3号が新設される（老人福祉事業等を営む者と社会福祉法第4条第3項の支援関係機関との連携に関する事項。努力義務）。令和9年4月1日施行</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
